--- a/astro-site/public/dl/haccp-templates/16-cooking-reheating-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/16-cooking-reheating-log.xlsx
@@ -580,7 +580,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>This is the monitoring log for the CCP of cooking and reheating prepared food. The hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)) points here: without this sheet, the most important CCP in the kitchen had nowhere to be documented.</t>
+          <t>This is the monitoring log for the CCP of cooking and reheating prepared food. The hazard analysis in template 12 (HACCP Plan) points here: without this sheet, the most important CCP in the kitchen had nowhere to be documented.</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>▸ The "Status" column calculates itself: OK in green when the center reaches the limit printed in the process name (165, 155, 145 or 135 °F), REPEAT in red below it. For reheating it also checks the time: more than 120 minutes to reach 165 °F is REPEAT even if it gets there.</t>
+          <t>▸ The "Status" column calculates itself: OK in green when the center reaches the limit printed in the process name (165, 155, 145 or 135 °F), REPEAT in red below it. For reheating it also checks the time: more than 120 minutes to reach 165 °F is REPEAT even if it gets there. If REPEAT is due to time (more than 2 h to reach 165 °F, §3-403.11(E)), discard it and log it in template 11 (Corrective Action Log).</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>▸ Reheating: 165 °F in the center AND reached within 2 hours (§3-403.11). It is the critical limit that your hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)) declares for this CCP.</t>
+          <t>▸ Reheating: 165 °F in the center AND reached within 2 hours (§3-403.11). It is the critical limit that your hazard analysis in template 12 (HACCP Plan) declares for this CCP.</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>▸ Fish that will be eaten raw, marinated or lightly cured is not cooked, it is frozen. That control goes in template 18 (Parasite Destruction Log (Fish Served Raw)).</t>
+          <t>▸ Fish that will be eaten raw, marinated or lightly cured is not cooked, it is frozen. That control goes in template 18 (Parasite Destruction Log).</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
     <row r="46" ht="12.2" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Criterion of the sheet: reach the limit shown in the process name in the CENTER of the item. If it says REPEAT, reheat it until it gets there and record the action; an item is never served while its verdict is red.</t>
+          <t>Criterion of the sheet: reach the limit shown in the process name in the CENTER of the item. If it says REPEAT for temperature, keep heating until it gets there and record the action; an item is never served while its verdict is red. If REPEAT is due to time (more than 2 h to reach 165 °F, §3-403.11(E)), discard it and log it in template 11 (Corrective Action Log).</t>
         </is>
       </c>
     </row>
@@ -1491,14 +1491,14 @@
     <row r="48" ht="24.5" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>The FDA Food Code sets minimum internal cooking temperatures by type of food (§3-401.11, §3-401.13) and 165 °F within 2 hours for reheating (§3-403.11). This kit applies those limits, which are also the critical limits in the hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)). UK: use the limits of your own HACCP plan.</t>
+          <t>The FDA Food Code sets minimum internal cooking temperatures by type of food (§3-401.11, §3-401.13) and 165 °F within 2 hours for reheating (§3-403.11). This kit applies those limits, which are also the critical limits in the hazard analysis, template 12 (HACCP Plan). UK: use the limits of your own HACCP plan.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="12.2" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Monitoring log for the cooking CCP of the hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)). If there is a deviation, open the incident in template 11 (Corrective Action Log).</t>
+          <t>Monitoring log for the cooking CCP of the hazard analysis in template 12 (HACCP Plan). If there is a deviation, open the incident in template 11 (Corrective Action Log).</t>
         </is>
       </c>
     </row>
